--- a/bookingkoala/JustNow-BookingKoala-Setup.xlsx
+++ b/bookingkoala/JustNow-BookingKoala-Setup.xlsx
@@ -139,7 +139,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Source: owner-approved price table (2 Oct 2026, amended 8-9 Oct) as loaded in the WhatsApp assistant. Prepared 23 Oct 2026. Yellow cells are for you to fill.</t>
+          <t xml:space="preserve">Source: owner-approved price table (2 Oct 2026, amended 8-9 Oct) as loaded in the WhatsApp assistant. Prepared 23 Oct 2026; area list extended and approved by the owner 23 Oct 2026. Yellow cells are for you to fill.</t>
         </is>
       </c>
     </row>
@@ -6566,17 +6566,12 @@
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Bay</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الخليج التجاري</t>
+          <t xml:space="preserve">Al Hudaiba</t>
         </is>
       </c>
       <c r="F55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone C</t>
+          <t xml:space="preserve">Zone B</t>
         </is>
       </c>
     </row>
@@ -6593,12 +6588,12 @@
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Downtown</t>
+          <t xml:space="preserve">Al Raffa</t>
         </is>
       </c>
       <c r="F56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone C</t>
+          <t xml:space="preserve">Zone B</t>
         </is>
       </c>
     </row>
@@ -6615,12 +6610,12 @@
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIFC</t>
+          <t xml:space="preserve">Al Mina (Port Rashid)</t>
         </is>
       </c>
       <c r="F57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone C</t>
+          <t xml:space="preserve">Zone B</t>
         </is>
       </c>
     </row>
@@ -6637,12 +6632,12 @@
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sheikh Zayed Road</t>
+          <t xml:space="preserve">Umm Hurair</t>
         </is>
       </c>
       <c r="F58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone C</t>
+          <t xml:space="preserve">Zone B</t>
         </is>
       </c>
     </row>
@@ -6659,12 +6654,12 @@
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">City Walk</t>
+          <t xml:space="preserve">Al Souk Al Kabeer</t>
         </is>
       </c>
       <c r="F59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone C</t>
+          <t xml:space="preserve">Zone B</t>
         </is>
       </c>
     </row>
@@ -6681,12 +6676,12 @@
       </c>
       <c r="C60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Wasl</t>
+          <t xml:space="preserve">Al Mushrif</t>
         </is>
       </c>
       <c r="F60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone C</t>
+          <t xml:space="preserve">Zone B</t>
         </is>
       </c>
     </row>
@@ -6703,12 +6698,12 @@
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Safa</t>
+          <t xml:space="preserve">Al Badia</t>
         </is>
       </c>
       <c r="F61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone C</t>
+          <t xml:space="preserve">Zone B</t>
         </is>
       </c>
     </row>
@@ -6725,17 +6720,12 @@
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jumeirah</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">جميرا</t>
+          <t xml:space="preserve">Culture Village</t>
         </is>
       </c>
       <c r="F62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone C</t>
+          <t xml:space="preserve">Zone B</t>
         </is>
       </c>
     </row>
@@ -6752,17 +6742,12 @@
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umm Suqeim</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">أم سقيم</t>
+          <t xml:space="preserve">Dubai Islands (Deira Islands)</t>
         </is>
       </c>
       <c r="F63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone C</t>
+          <t xml:space="preserve">Zone B</t>
         </is>
       </c>
     </row>
@@ -6779,12 +6764,12 @@
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Manara</t>
+          <t xml:space="preserve">Academic City</t>
         </is>
       </c>
       <c r="F64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone C</t>
+          <t xml:space="preserve">Zone B</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6786,12 @@
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Sufouh</t>
+          <t xml:space="preserve">Business Bay</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الصفوح</t>
+          <t xml:space="preserve">الخليج التجاري</t>
         </is>
       </c>
       <c r="F65" s="0" t="inlineStr">
@@ -6828,12 +6813,7 @@
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Barsha</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">البرشاء</t>
+          <t xml:space="preserve">Downtown</t>
         </is>
       </c>
       <c r="F66" s="0" t="inlineStr">
@@ -6855,7 +6835,7 @@
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Barsha South</t>
+          <t xml:space="preserve">DIFC</t>
         </is>
       </c>
       <c r="F67" s="0" t="inlineStr">
@@ -6877,7 +6857,7 @@
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">TECOM</t>
+          <t xml:space="preserve">Sheikh Zayed Road</t>
         </is>
       </c>
       <c r="F68" s="0" t="inlineStr">
@@ -6899,7 +6879,7 @@
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dubai Media City</t>
+          <t xml:space="preserve">City Walk</t>
         </is>
       </c>
       <c r="F69" s="0" t="inlineStr">
@@ -6921,7 +6901,7 @@
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dubai Internet City</t>
+          <t xml:space="preserve">Al Wasl</t>
         </is>
       </c>
       <c r="F70" s="0" t="inlineStr">
@@ -6943,7 +6923,7 @@
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knowledge Park</t>
+          <t xml:space="preserve">Al Safa</t>
         </is>
       </c>
       <c r="F71" s="0" t="inlineStr">
@@ -6965,17 +6945,12 @@
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dubai Marina</t>
+          <t xml:space="preserve">Jumeirah</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">المرينا</t>
-        </is>
-      </c>
-      <c r="E72" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Marina</t>
+          <t xml:space="preserve">جميرا</t>
         </is>
       </c>
       <c r="F72" s="0" t="inlineStr">
@@ -6997,12 +6972,12 @@
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBR</t>
-        </is>
-      </c>
-      <c r="E73" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jumeirah Beach Residence</t>
+          <t xml:space="preserve">Umm Suqeim</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أم سقيم</t>
         </is>
       </c>
       <c r="F73" s="0" t="inlineStr">
@@ -7024,7 +6999,7 @@
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bluewaters Island</t>
+          <t xml:space="preserve">Al Manara</t>
         </is>
       </c>
       <c r="F74" s="0" t="inlineStr">
@@ -7046,12 +7021,12 @@
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Palm Jumeirah</t>
+          <t xml:space="preserve">Al Sufouh</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">نخلة جميرا</t>
+          <t xml:space="preserve">الصفوح</t>
         </is>
       </c>
       <c r="F75" s="0" t="inlineStr">
@@ -7073,12 +7048,12 @@
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">JLT</t>
-        </is>
-      </c>
-      <c r="E76" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jumeirah Lake Towers</t>
+          <t xml:space="preserve">Al Barsha</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">البرشاء</t>
         </is>
       </c>
       <c r="F76" s="0" t="inlineStr">
@@ -7100,12 +7075,7 @@
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">JVC</t>
-        </is>
-      </c>
-      <c r="E77" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jumeirah Village Circle</t>
+          <t xml:space="preserve">Al Barsha South</t>
         </is>
       </c>
       <c r="F77" s="0" t="inlineStr">
@@ -7127,12 +7097,7 @@
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">JVT</t>
-        </is>
-      </c>
-      <c r="E78" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jumeirah Village Triangle</t>
+          <t xml:space="preserve">TECOM</t>
         </is>
       </c>
       <c r="F78" s="0" t="inlineStr">
@@ -7154,12 +7119,7 @@
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Furjan</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الفرجان</t>
+          <t xml:space="preserve">Dubai Media City</t>
         </is>
       </c>
       <c r="F79" s="0" t="inlineStr">
@@ -7181,7 +7141,7 @@
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discovery Gardens</t>
+          <t xml:space="preserve">Dubai Internet City</t>
         </is>
       </c>
       <c r="F80" s="0" t="inlineStr">
@@ -7203,7 +7163,7 @@
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Gardens</t>
+          <t xml:space="preserve">Knowledge Park</t>
         </is>
       </c>
       <c r="F81" s="0" t="inlineStr">
@@ -7225,12 +7185,17 @@
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jebel Ali</t>
+          <t xml:space="preserve">Dubai Marina</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">جبل علي</t>
+          <t xml:space="preserve">المرينا</t>
+        </is>
+      </c>
+      <c r="E82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marina</t>
         </is>
       </c>
       <c r="F82" s="0" t="inlineStr">
@@ -7252,12 +7217,12 @@
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dubai Investment Park</t>
+          <t xml:space="preserve">JBR</t>
         </is>
       </c>
       <c r="E83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIP</t>
+          <t xml:space="preserve">Jumeirah Beach Residence</t>
         </is>
       </c>
       <c r="F83" s="0" t="inlineStr">
@@ -7279,7 +7244,7 @@
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Community</t>
+          <t xml:space="preserve">Bluewaters Island</t>
         </is>
       </c>
       <c r="F84" s="0" t="inlineStr">
@@ -7301,7 +7266,12 @@
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Springs</t>
+          <t xml:space="preserve">Palm Jumeirah</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">نخلة جميرا</t>
         </is>
       </c>
       <c r="F85" s="0" t="inlineStr">
@@ -7323,7 +7293,12 @@
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Meadows</t>
+          <t xml:space="preserve">JLT</t>
+        </is>
+      </c>
+      <c r="E86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jumeirah Lake Towers</t>
         </is>
       </c>
       <c r="F86" s="0" t="inlineStr">
@@ -7345,7 +7320,12 @@
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Lakes</t>
+          <t xml:space="preserve">JVC</t>
+        </is>
+      </c>
+      <c r="E87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jumeirah Village Circle</t>
         </is>
       </c>
       <c r="F87" s="0" t="inlineStr">
@@ -7367,7 +7347,12 @@
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Greens</t>
+          <t xml:space="preserve">JVT</t>
+        </is>
+      </c>
+      <c r="E88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jumeirah Village Triangle</t>
         </is>
       </c>
       <c r="F88" s="0" t="inlineStr">
@@ -7389,7 +7374,12 @@
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Views</t>
+          <t xml:space="preserve">Al Furjan</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفرجان</t>
         </is>
       </c>
       <c r="F89" s="0" t="inlineStr">
@@ -7411,7 +7401,7 @@
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emirates Hills</t>
+          <t xml:space="preserve">Discovery Gardens</t>
         </is>
       </c>
       <c r="F90" s="0" t="inlineStr">
@@ -7433,7 +7423,7 @@
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jumeirah Islands</t>
+          <t xml:space="preserve">The Gardens</t>
         </is>
       </c>
       <c r="F91" s="0" t="inlineStr">
@@ -7455,7 +7445,12 @@
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jumeirah Park</t>
+          <t xml:space="preserve">Jebel Ali</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">جبل علي</t>
         </is>
       </c>
       <c r="F92" s="0" t="inlineStr">
@@ -7477,7 +7472,12 @@
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Khail Heights</t>
+          <t xml:space="preserve">Dubai Investment Park</t>
+        </is>
+      </c>
+      <c r="E93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIP</t>
         </is>
       </c>
       <c r="F93" s="0" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dubai Hills</t>
+          <t xml:space="preserve">Green Community</t>
         </is>
       </c>
       <c r="F94" s="0" t="inlineStr">
@@ -7521,12 +7521,7 @@
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arabian Ranches</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">المرابع العربية</t>
+          <t xml:space="preserve">The Springs</t>
         </is>
       </c>
       <c r="F95" s="0" t="inlineStr">
@@ -7548,7 +7543,7 @@
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor City</t>
+          <t xml:space="preserve">The Meadows</t>
         </is>
       </c>
       <c r="F96" s="0" t="inlineStr">
@@ -7570,7 +7565,7 @@
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sports City</t>
+          <t xml:space="preserve">The Lakes</t>
         </is>
       </c>
       <c r="F97" s="0" t="inlineStr">
@@ -7592,7 +7587,7 @@
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Studio City</t>
+          <t xml:space="preserve">The Greens</t>
         </is>
       </c>
       <c r="F98" s="0" t="inlineStr">
@@ -7614,12 +7609,7 @@
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production City (IMPZ)</t>
-        </is>
-      </c>
-      <c r="E99" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IMPZ</t>
+          <t xml:space="preserve">The Views</t>
         </is>
       </c>
       <c r="F99" s="0" t="inlineStr">
@@ -7641,7 +7631,7 @@
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arjan</t>
+          <t xml:space="preserve">Emirates Hills</t>
         </is>
       </c>
       <c r="F100" s="0" t="inlineStr">
@@ -7663,7 +7653,7 @@
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Majan</t>
+          <t xml:space="preserve">Jumeirah Islands</t>
         </is>
       </c>
       <c r="F101" s="0" t="inlineStr">
@@ -7685,22 +7675,12 @@
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dubailand (Arabian Ranches / Global Village side)</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">دبي لاند</t>
+          <t xml:space="preserve">Jumeirah Park</t>
         </is>
       </c>
       <c r="F102" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Zone C</t>
-        </is>
-      </c>
-      <c r="G102" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">If the customer says only 'Dubailand', ask which side. Silicon Oasis side = Zone B (DLRC, Liwan, Wadi Al Safa, Queue Point, Skycourts).</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7697,7 @@
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mudon</t>
+          <t xml:space="preserve">Al Khail Heights</t>
         </is>
       </c>
       <c r="F103" s="0" t="inlineStr">
@@ -7739,7 +7719,7 @@
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remraam</t>
+          <t xml:space="preserve">Dubai Hills</t>
         </is>
       </c>
       <c r="F104" s="0" t="inlineStr">
@@ -7761,7 +7741,12 @@
       </c>
       <c r="C105" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damac Hills</t>
+          <t xml:space="preserve">Arabian Ranches</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">المرابع العربية</t>
         </is>
       </c>
       <c r="F105" s="0" t="inlineStr">
@@ -7783,7 +7768,7 @@
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Town Square</t>
+          <t xml:space="preserve">Motor City</t>
         </is>
       </c>
       <c r="F106" s="0" t="inlineStr">
@@ -7805,7 +7790,7 @@
       </c>
       <c r="C107" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tilal Al Ghaf</t>
+          <t xml:space="preserve">Sports City</t>
         </is>
       </c>
       <c r="F107" s="0" t="inlineStr">
@@ -7827,7 +7812,7 @@
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serena</t>
+          <t xml:space="preserve">Studio City</t>
         </is>
       </c>
       <c r="F108" s="0" t="inlineStr">
@@ -7849,7 +7834,12 @@
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Villanova</t>
+          <t xml:space="preserve">Production City (IMPZ)</t>
+        </is>
+      </c>
+      <c r="E109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMPZ</t>
         </is>
       </c>
       <c r="F109" s="0" t="inlineStr">
@@ -7871,7 +7861,7 @@
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mira</t>
+          <t xml:space="preserve">Arjan</t>
         </is>
       </c>
       <c r="F110" s="0" t="inlineStr">
@@ -7893,7 +7883,7 @@
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reem</t>
+          <t xml:space="preserve">Majan</t>
         </is>
       </c>
       <c r="F111" s="0" t="inlineStr">
@@ -7915,12 +7905,22 @@
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Sustainable City</t>
+          <t xml:space="preserve">Dubailand (Arabian Ranches / Global Village side)</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">دبي لاند</t>
         </is>
       </c>
       <c r="F112" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Zone C</t>
+        </is>
+      </c>
+      <c r="G112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If the customer says only 'Dubailand', ask which side. Silicon Oasis side = Zone B (DLRC, Liwan, Wadi Al Safa, Queue Point, Skycourts).</t>
         </is>
       </c>
     </row>
@@ -7937,12 +7937,7 @@
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meydan</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ميدان</t>
+          <t xml:space="preserve">Mudon</t>
         </is>
       </c>
       <c r="F113" s="0" t="inlineStr">
@@ -7964,7 +7959,7 @@
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nad Al Sheba</t>
+          <t xml:space="preserve">Remraam</t>
         </is>
       </c>
       <c r="F114" s="0" t="inlineStr">
@@ -7986,7 +7981,7 @@
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Barari</t>
+          <t xml:space="preserve">Damac Hills</t>
         </is>
       </c>
       <c r="F115" s="0" t="inlineStr">
@@ -8008,7 +8003,7 @@
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dubai Creek Harbour</t>
+          <t xml:space="preserve">Town Square</t>
         </is>
       </c>
       <c r="F116" s="0" t="inlineStr">
@@ -8030,7 +8025,7 @@
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dubai Festival City</t>
+          <t xml:space="preserve">Tilal Al Ghaf</t>
         </is>
       </c>
       <c r="F117" s="0" t="inlineStr">
@@ -8052,7 +8047,7 @@
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Academic City</t>
+          <t xml:space="preserve">Serena</t>
         </is>
       </c>
       <c r="F118" s="0" t="inlineStr">
@@ -8074,7 +8069,7 @@
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dubai South</t>
+          <t xml:space="preserve">Villanova</t>
         </is>
       </c>
       <c r="F119" s="0" t="inlineStr">
@@ -8096,7 +8091,7 @@
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lehbab</t>
+          <t xml:space="preserve">Mira</t>
         </is>
       </c>
       <c r="F120" s="0" t="inlineStr">
@@ -8118,12 +8113,7 @@
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hatta</t>
-        </is>
-      </c>
-      <c r="D121" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">حتا</t>
+          <t xml:space="preserve">Reem</t>
         </is>
       </c>
       <c r="F121" s="0" t="inlineStr">
@@ -8135,691 +8125,626 @@
     <row r="122">
       <c r="A122" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Nahda (Sharjah)</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">النهدة</t>
+          <t xml:space="preserve">The Sustainable City</t>
         </is>
       </c>
       <c r="F122" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Majaz</t>
+          <t xml:space="preserve">Meydan</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">المجاز</t>
+          <t xml:space="preserve">ميدان</t>
         </is>
       </c>
       <c r="F123" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Taawun</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">التعاون</t>
+          <t xml:space="preserve">Nad Al Sheba</t>
         </is>
       </c>
       <c r="F124" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Khan</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الخان</t>
+          <t xml:space="preserve">Al Barari</t>
         </is>
       </c>
       <c r="F125" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Qasimia</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">القاسمية</t>
+          <t xml:space="preserve">Dubai Creek Harbour</t>
         </is>
       </c>
       <c r="F126" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Mamzar (Sharjah)</t>
-        </is>
-      </c>
-      <c r="D127" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الممزر</t>
+          <t xml:space="preserve">Dubai Festival City</t>
         </is>
       </c>
       <c r="F127" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Qulayaah</t>
+          <t xml:space="preserve">Dubai South</t>
         </is>
       </c>
       <c r="F128" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Ghuwair</t>
-        </is>
-      </c>
-      <c r="D129" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الغوير</t>
+          <t xml:space="preserve">Mohammed Bin Rashid City (MBR City)</t>
         </is>
       </c>
       <c r="F129" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolla</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">رولا</t>
+          <t xml:space="preserve">Sobha Hartland</t>
         </is>
       </c>
       <c r="F130" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abu Shagara</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">أبو شغارة</t>
+          <t xml:space="preserve">District One</t>
         </is>
       </c>
       <c r="F131" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Nabba</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">النباعة</t>
+          <t xml:space="preserve">Dubai Science Park</t>
         </is>
       </c>
       <c r="F132" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Mujarrah</t>
+          <t xml:space="preserve">Jumeirah Golf Estates</t>
         </is>
       </c>
       <c r="F133" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Soor</t>
+          <t xml:space="preserve">Jumeirah Heights</t>
         </is>
       </c>
       <c r="F134" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bu Daniq</t>
+          <t xml:space="preserve">Dubai Harbour</t>
         </is>
       </c>
       <c r="F135" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Mirgab</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">المرقاب</t>
+          <t xml:space="preserve">La Mer</t>
         </is>
       </c>
       <c r="F136" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Layyah</t>
+          <t xml:space="preserve">Pearl Jumeirah</t>
         </is>
       </c>
       <c r="F137" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Khaledia</t>
-        </is>
-      </c>
-      <c r="D138" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الخالدية</t>
+          <t xml:space="preserve">Umm Al Sheif</t>
         </is>
       </c>
       <c r="F138" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Heerah</t>
+          <t xml:space="preserve">Dubai Design District (d3)</t>
         </is>
       </c>
       <c r="F139" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Fisht</t>
+          <t xml:space="preserve">Expo City</t>
         </is>
       </c>
       <c r="F140" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maysaloon</t>
+          <t xml:space="preserve">Dubai Industrial City</t>
         </is>
       </c>
       <c r="F141" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Jazzat</t>
+          <t xml:space="preserve">The Villa</t>
         </is>
       </c>
       <c r="F142" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Shahba</t>
+          <t xml:space="preserve">Falcon City</t>
         </is>
       </c>
       <c r="F143" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Gharb</t>
+          <t xml:space="preserve">Rukan</t>
         </is>
       </c>
       <c r="F144" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Sharq</t>
+          <t xml:space="preserve">Damac Lagoons</t>
         </is>
       </c>
       <c r="F145" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Yarmook</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">اليرموك</t>
+          <t xml:space="preserve">Damac Hills 2 (Akoya)</t>
         </is>
       </c>
       <c r="F146" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Rifaa</t>
-        </is>
-      </c>
-      <c r="D147" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الرفاع</t>
+          <t xml:space="preserve">Palm Jebel Ali</t>
         </is>
       </c>
       <c r="F147" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Nasserya</t>
-        </is>
-      </c>
-      <c r="D148" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الناصرية</t>
+          <t xml:space="preserve">Lehbab</t>
         </is>
       </c>
       <c r="F148" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Dubai</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">دبي</t>
         </is>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Khezamia</t>
+          <t xml:space="preserve">Hatta</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">حتا</t>
         </is>
       </c>
       <c r="F149" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone A</t>
+          <t xml:space="preserve">Zone C</t>
         </is>
       </c>
     </row>
@@ -8836,7 +8761,12 @@
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharqan</t>
+          <t xml:space="preserve">Al Nahda (Sharjah)</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النهدة</t>
         </is>
       </c>
       <c r="F150" s="0" t="inlineStr">
@@ -8858,7 +8788,12 @@
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samnan</t>
+          <t xml:space="preserve">Al Majaz</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">المجاز</t>
         </is>
       </c>
       <c r="F151" s="0" t="inlineStr">
@@ -8880,7 +8815,12 @@
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Goaz</t>
+          <t xml:space="preserve">Al Taawun</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">التعاون</t>
         </is>
       </c>
       <c r="F152" s="0" t="inlineStr">
@@ -8902,7 +8842,12 @@
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halwan</t>
+          <t xml:space="preserve">Al Khan</t>
+        </is>
+      </c>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الخان</t>
         </is>
       </c>
       <c r="F153" s="0" t="inlineStr">
@@ -8924,7 +8869,12 @@
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Azra</t>
+          <t xml:space="preserve">Al Qasimia</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">القاسمية</t>
         </is>
       </c>
       <c r="F154" s="0" t="inlineStr">
@@ -8946,7 +8896,12 @@
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Ramtha</t>
+          <t xml:space="preserve">Al Mamzar (Sharjah)</t>
+        </is>
+      </c>
+      <c r="D155" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الممزر</t>
         </is>
       </c>
       <c r="F155" s="0" t="inlineStr">
@@ -8968,12 +8923,7 @@
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Muwaileh</t>
-        </is>
-      </c>
-      <c r="D156" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">مويلح</t>
+          <t xml:space="preserve">Al Qulayaah</t>
         </is>
       </c>
       <c r="F156" s="0" t="inlineStr">
@@ -8995,12 +8945,12 @@
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Zahia</t>
+          <t xml:space="preserve">Al Ghuwair</t>
         </is>
       </c>
       <c r="D157" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الزاهية</t>
+          <t xml:space="preserve">الغوير</t>
         </is>
       </c>
       <c r="F157" s="0" t="inlineStr">
@@ -9022,7 +8972,12 @@
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tilal City</t>
+          <t xml:space="preserve">Rolla</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رولا</t>
         </is>
       </c>
       <c r="F158" s="0" t="inlineStr">
@@ -9044,7 +8999,12 @@
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">University City</t>
+          <t xml:space="preserve">Abu Shagara</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أبو شغارة</t>
         </is>
       </c>
       <c r="F159" s="0" t="inlineStr">
@@ -9066,7 +9026,12 @@
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nasma Residences</t>
+          <t xml:space="preserve">Al Nabba</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النباعة</t>
         </is>
       </c>
       <c r="F160" s="0" t="inlineStr">
@@ -9088,7 +9053,7 @@
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah Sustainable City</t>
+          <t xml:space="preserve">Al Mujarrah</t>
         </is>
       </c>
       <c r="F161" s="0" t="inlineStr">
@@ -9110,7 +9075,7 @@
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrial Area</t>
+          <t xml:space="preserve">Al Soor</t>
         </is>
       </c>
       <c r="F162" s="0" t="inlineStr">
@@ -9132,7 +9097,7 @@
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maliha Road</t>
+          <t xml:space="preserve">Bu Daniq</t>
         </is>
       </c>
       <c r="F163" s="0" t="inlineStr">
@@ -9154,22 +9119,17 @@
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Suyoh</t>
+          <t xml:space="preserve">Al Mirgab</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">السيوح</t>
+          <t xml:space="preserve">المرقاب</t>
         </is>
       </c>
       <c r="F164" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone E</t>
-        </is>
-      </c>
-      <c r="G164" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Far from base: Zone E price (owner decision 28 Sep 2026).</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
@@ -9186,17 +9146,12 @@
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Tai</t>
-        </is>
-      </c>
-      <c r="D165" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الطي</t>
+          <t xml:space="preserve">Al Layyah</t>
         </is>
       </c>
       <c r="F165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone E</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
@@ -9213,17 +9168,17 @@
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Rahmaniya</t>
+          <t xml:space="preserve">Al Khaledia</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الرحمانية</t>
+          <t xml:space="preserve">الخالدية</t>
         </is>
       </c>
       <c r="F166" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone E</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
@@ -9240,12 +9195,12 @@
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Barashi</t>
+          <t xml:space="preserve">Al Heerah</t>
         </is>
       </c>
       <c r="F167" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone E</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
@@ -9262,12 +9217,12 @@
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hoshi</t>
+          <t xml:space="preserve">Al Fisht</t>
         </is>
       </c>
       <c r="F168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone E</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
@@ -9284,12 +9239,12 @@
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Juraina</t>
+          <t xml:space="preserve">Maysaloon</t>
         </is>
       </c>
       <c r="F169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone E</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
@@ -9306,12 +9261,12 @@
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Qarayen</t>
+          <t xml:space="preserve">Al Jazzat</t>
         </is>
       </c>
       <c r="F170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone E</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
@@ -9328,12 +9283,12 @@
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Sajaa</t>
+          <t xml:space="preserve">Al Shahba</t>
         </is>
       </c>
       <c r="F171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone E</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
@@ -9350,17 +9305,12 @@
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Hamriyah</t>
-        </is>
-      </c>
-      <c r="D172" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الحمرية</t>
+          <t xml:space="preserve">Al Gharb</t>
         </is>
       </c>
       <c r="F172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone E</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
@@ -9377,22 +9327,12 @@
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mleiha</t>
-        </is>
-      </c>
-      <c r="D173" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">مليحة</t>
+          <t xml:space="preserve">Al Sharq</t>
         </is>
       </c>
       <c r="F173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G173" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
@@ -9409,22 +9349,17 @@
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Dhaid</t>
+          <t xml:space="preserve">Al Yarmook</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الذيد</t>
+          <t xml:space="preserve">اليرموك</t>
         </is>
       </c>
       <c r="F174" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G174" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
@@ -9441,22 +9376,17 @@
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Madam</t>
+          <t xml:space="preserve">Al Rifaa</t>
         </is>
       </c>
       <c r="D175" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">المدام</t>
+          <t xml:space="preserve">الرفاع</t>
         </is>
       </c>
       <c r="F175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G175" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
@@ -9473,17 +9403,17 @@
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Batayah</t>
+          <t xml:space="preserve">Al Nasserya</t>
+        </is>
+      </c>
+      <c r="D176" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الناصرية</t>
         </is>
       </c>
       <c r="F176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G176" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
@@ -9500,22 +9430,12 @@
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalba</t>
-        </is>
-      </c>
-      <c r="D177" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">كلباء</t>
+          <t xml:space="preserve">Al Khezamia</t>
         </is>
       </c>
       <c r="F177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G177" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
@@ -9532,22 +9452,12 @@
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Khorfakkan</t>
-        </is>
-      </c>
-      <c r="D178" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">خورفكان</t>
+          <t xml:space="preserve">Sharqan</t>
         </is>
       </c>
       <c r="F178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G178" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
@@ -9564,44 +9474,29 @@
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dibba Al Hisn</t>
+          <t xml:space="preserve">Samnan</t>
         </is>
       </c>
       <c r="F179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G179" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Nuaimiya</t>
-        </is>
-      </c>
-      <c r="D180" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">النعيمية</t>
-        </is>
-      </c>
-      <c r="E180" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Al Nuaimiya 1-3 / Al Nuaimiyah</t>
+          <t xml:space="preserve">Al Goaz</t>
         </is>
       </c>
       <c r="F180" s="0" t="inlineStr">
@@ -9613,27 +9508,17 @@
     <row r="181">
       <c r="A181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Rashidiya</t>
-        </is>
-      </c>
-      <c r="D181" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الراشدية</t>
-        </is>
-      </c>
-      <c r="E181" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Al Rashidiya 1-3</t>
+          <t xml:space="preserve">Halwan</t>
         </is>
       </c>
       <c r="F181" s="0" t="inlineStr">
@@ -9645,22 +9530,17 @@
     <row r="182">
       <c r="A182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Jurf</t>
-        </is>
-      </c>
-      <c r="D182" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الجرف</t>
+          <t xml:space="preserve">Al Azra</t>
         </is>
       </c>
       <c r="F182" s="0" t="inlineStr">
@@ -9672,17 +9552,17 @@
     <row r="183">
       <c r="A183" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman Corniche</t>
+          <t xml:space="preserve">Al Ramtha</t>
         </is>
       </c>
       <c r="F183" s="0" t="inlineStr">
@@ -9694,17 +9574,22 @@
     <row r="184">
       <c r="A184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman Downtown</t>
+          <t xml:space="preserve">Muwaileh</t>
+        </is>
+      </c>
+      <c r="D184" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مويلح</t>
         </is>
       </c>
       <c r="F184" s="0" t="inlineStr">
@@ -9716,27 +9601,22 @@
     <row r="185">
       <c r="A185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Mowaihat</t>
+          <t xml:space="preserve">Al Zahia</t>
         </is>
       </c>
       <c r="D185" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">المويهات</t>
-        </is>
-      </c>
-      <c r="E185" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Al Mowaihat 1-3 / Al Mowaihat</t>
+          <t xml:space="preserve">الزاهية</t>
         </is>
       </c>
       <c r="F185" s="0" t="inlineStr">
@@ -9748,22 +9628,17 @@
     <row r="186">
       <c r="A186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Hamidiya</t>
-        </is>
-      </c>
-      <c r="D186" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الحميدية</t>
+          <t xml:space="preserve">Tilal City</t>
         </is>
       </c>
       <c r="F186" s="0" t="inlineStr">
@@ -9775,27 +9650,17 @@
     <row r="187">
       <c r="A187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Rawda</t>
-        </is>
-      </c>
-      <c r="D187" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الروضة</t>
-        </is>
-      </c>
-      <c r="E187" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Al Rawda 1-3</t>
+          <t xml:space="preserve">University City</t>
         </is>
       </c>
       <c r="F187" s="0" t="inlineStr">
@@ -9807,17 +9672,17 @@
     <row r="188">
       <c r="A188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emirates City</t>
+          <t xml:space="preserve">Nasma Residences</t>
         </is>
       </c>
       <c r="F188" s="0" t="inlineStr">
@@ -9829,17 +9694,17 @@
     <row r="189">
       <c r="A189" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Zahya</t>
+          <t xml:space="preserve">Sharjah Sustainable City</t>
         </is>
       </c>
       <c r="F189" s="0" t="inlineStr">
@@ -9851,17 +9716,17 @@
     <row r="190">
       <c r="A190" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Yasmeen</t>
+          <t xml:space="preserve">Industrial Area</t>
         </is>
       </c>
       <c r="F190" s="0" t="inlineStr">
@@ -9873,17 +9738,17 @@
     <row r="191">
       <c r="A191" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Nakheel</t>
+          <t xml:space="preserve">Maliha Road</t>
         </is>
       </c>
       <c r="F191" s="0" t="inlineStr">
@@ -9895,22 +9760,17 @@
     <row r="192">
       <c r="A192" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Rumailah</t>
-        </is>
-      </c>
-      <c r="D192" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الرميلة</t>
+          <t xml:space="preserve">Al Butina</t>
         </is>
       </c>
       <c r="F192" s="0" t="inlineStr">
@@ -9922,17 +9782,17 @@
     <row r="193">
       <c r="A193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Bustan</t>
+          <t xml:space="preserve">Al Qadisiya</t>
         </is>
       </c>
       <c r="F193" s="0" t="inlineStr">
@@ -9944,17 +9804,17 @@
     <row r="194">
       <c r="A194" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Sawan</t>
+          <t xml:space="preserve">Al Falaj</t>
         </is>
       </c>
       <c r="F194" s="0" t="inlineStr">
@@ -9966,17 +9826,17 @@
     <row r="195">
       <c r="A195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Mushairef</t>
+          <t xml:space="preserve">Al Manakh</t>
         </is>
       </c>
       <c r="F195" s="0" t="inlineStr">
@@ -9988,17 +9848,17 @@
     <row r="196">
       <c r="A196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Helio</t>
+          <t xml:space="preserve">Al Musalla</t>
         </is>
       </c>
       <c r="F196" s="0" t="inlineStr">
@@ -10010,17 +9870,17 @@
     <row r="197">
       <c r="A197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Alia</t>
+          <t xml:space="preserve">Al Shuwaihean</t>
         </is>
       </c>
       <c r="F197" s="0" t="inlineStr">
@@ -10032,17 +9892,17 @@
     <row r="198">
       <c r="A198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Tallah</t>
+          <t xml:space="preserve">Al Mareija</t>
         </is>
       </c>
       <c r="F198" s="0" t="inlineStr">
@@ -10054,17 +9914,17 @@
     <row r="199">
       <c r="A199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Amerah</t>
+          <t xml:space="preserve">Al Nud</t>
         </is>
       </c>
       <c r="F199" s="0" t="inlineStr">
@@ -10076,17 +9936,17 @@
     <row r="200">
       <c r="A200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Hamriya (Ajman)</t>
+          <t xml:space="preserve">Al Ghubaiba</t>
         </is>
       </c>
       <c r="F200" s="0" t="inlineStr">
@@ -10098,22 +9958,17 @@
     <row r="201">
       <c r="A201" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Zorah</t>
-        </is>
-      </c>
-      <c r="D201" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الزوراء</t>
+          <t xml:space="preserve">Al Jubail</t>
         </is>
       </c>
       <c r="F201" s="0" t="inlineStr">
@@ -10125,17 +9980,17 @@
     <row r="202">
       <c r="A202" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Garden City</t>
+          <t xml:space="preserve">Al Fayha</t>
         </is>
       </c>
       <c r="F202" s="0" t="inlineStr">
@@ -10147,17 +10002,17 @@
     <row r="203">
       <c r="A203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman Uptown</t>
+          <t xml:space="preserve">Al Darari</t>
         </is>
       </c>
       <c r="F203" s="0" t="inlineStr">
@@ -10169,17 +10024,17 @@
     <row r="204">
       <c r="A204" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman Industrial Area</t>
+          <t xml:space="preserve">Al Yash</t>
         </is>
       </c>
       <c r="F204" s="0" t="inlineStr">
@@ -10191,613 +10046,553 @@
     <row r="205">
       <c r="A205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B205" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Masfout</t>
-        </is>
-      </c>
-      <c r="D205" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">مصفوت</t>
+          <t xml:space="preserve">Al Abar</t>
         </is>
       </c>
       <c r="F205" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G205" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajman</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">عجمان</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manama</t>
-        </is>
-      </c>
-      <c r="D206" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">المنامة</t>
+          <t xml:space="preserve">Al Sweihat</t>
         </is>
       </c>
       <c r="F206" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G206" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umm Al Quwain</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">أم القيوين</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umm Al Quwain City</t>
+          <t xml:space="preserve">Al Falah</t>
         </is>
       </c>
       <c r="F207" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone B</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umm Al Quwain</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">أم القيوين</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Salamah</t>
+          <t xml:space="preserve">Al Riqa (Sharjah)</t>
         </is>
       </c>
       <c r="F208" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone B</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umm Al Quwain</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">أم القيوين</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Raas</t>
+          <t xml:space="preserve">Al Qasba</t>
         </is>
       </c>
       <c r="F209" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone B</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umm Al Quwain</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">أم القيوين</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Haditha</t>
+          <t xml:space="preserve">Maryam Island</t>
         </is>
       </c>
       <c r="F210" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone B</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umm Al Quwain</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">أم القيوين</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C211" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Riqqah</t>
+          <t xml:space="preserve">Al Mamsha</t>
         </is>
       </c>
       <c r="F211" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone B</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umm Al Quwain</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">أم القيوين</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Ramlah</t>
+          <t xml:space="preserve">Aljada</t>
         </is>
       </c>
       <c r="F212" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone B</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umm Al Quwain</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B213" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">أم القيوين</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Humrah</t>
+          <t xml:space="preserve">Wasit</t>
         </is>
       </c>
       <c r="F213" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone B</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umm Al Quwain</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">أم القيوين</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Dar Al Baida</t>
+          <t xml:space="preserve">Al Nouf</t>
         </is>
       </c>
       <c r="F214" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone B</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umm Al Quwain</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B215" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">أم القيوين</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAQ Marina</t>
+          <t xml:space="preserve">Al Zubair</t>
         </is>
       </c>
       <c r="F215" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone B</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umm Al Quwain</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">أم القيوين</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C216" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emirates Modern Industrial Area</t>
+          <t xml:space="preserve">Al Mahatta</t>
         </is>
       </c>
       <c r="F216" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone B</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umm Al Quwain</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B217" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">أم القيوين</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C217" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falaj Al Mualla</t>
-        </is>
-      </c>
-      <c r="D217" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">فلج المعلا</t>
+          <t xml:space="preserve">Al Ghafiya</t>
         </is>
       </c>
       <c r="F217" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G217" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ras Al Khaimah</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">رأس الخيمة</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ras Al Khaimah City</t>
+          <t xml:space="preserve">Al Suyoh</t>
+        </is>
+      </c>
+      <c r="D218" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">السيوح</t>
         </is>
       </c>
       <c r="F218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
+          <t xml:space="preserve">Zone E</t>
         </is>
       </c>
       <c r="G218" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Far from base: Zone E price (owner decision 28 Sep 2026).</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ras Al Khaimah</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B219" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">رأس الخيمة</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Nakheel</t>
+          <t xml:space="preserve">Al Tai</t>
+        </is>
+      </c>
+      <c r="D219" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الطي</t>
         </is>
       </c>
       <c r="F219" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G219" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone E</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ras Al Khaimah</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">رأس الخيمة</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Dhait</t>
+          <t xml:space="preserve">Al Rahmaniya</t>
+        </is>
+      </c>
+      <c r="D220" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الرحمانية</t>
         </is>
       </c>
       <c r="F220" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G220" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone E</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ras Al Khaimah</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B221" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">رأس الخيمة</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Mairid</t>
+          <t xml:space="preserve">Al Barashi</t>
         </is>
       </c>
       <c r="F221" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G221" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone E</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ras Al Khaimah</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">رأس الخيمة</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Uraibi</t>
+          <t xml:space="preserve">Hoshi</t>
         </is>
       </c>
       <c r="F222" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G222" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone E</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ras Al Khaimah</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">رأس الخيمة</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Khuzam</t>
+          <t xml:space="preserve">Al Juraina</t>
         </is>
       </c>
       <c r="F223" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G223" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone E</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ras Al Khaimah</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">رأس الخيمة</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C224" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Qusaidat</t>
+          <t xml:space="preserve">Al Qarayen</t>
         </is>
       </c>
       <c r="F224" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G224" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone E</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ras Al Khaimah</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B225" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">رأس الخيمة</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Hamra Village</t>
+          <t xml:space="preserve">Al Sajaa</t>
         </is>
       </c>
       <c r="F225" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G225" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone E</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ras Al Khaimah</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">رأس الخيمة</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mina Al Arab</t>
+          <t xml:space="preserve">Al Hamriyah</t>
+        </is>
+      </c>
+      <c r="D226" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الحمرية</t>
         </is>
       </c>
       <c r="F226" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G226" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone E</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ras Al Khaimah</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B227" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">رأس الخيمة</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C227" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Jazirah Al Hamra</t>
-        </is>
-      </c>
-      <c r="D227" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الجزيرة الحمراء</t>
+          <t xml:space="preserve">Al Sehma</t>
         </is>
       </c>
       <c r="F227" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G227" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone E</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ras Al Khaimah</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B228" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">رأس الخيمة</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C228" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Rams</t>
+          <t xml:space="preserve">Mleiha</t>
         </is>
       </c>
       <c r="D228" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الرمس</t>
+          <t xml:space="preserve">مليحة</t>
         </is>
       </c>
       <c r="F228" s="0" t="inlineStr">
@@ -10814,17 +10609,22 @@
     <row r="229">
       <c r="A229" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ras Al Khaimah</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B229" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">رأس الخيمة</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C229" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digdaga</t>
+          <t xml:space="preserve">Al Dhaid</t>
+        </is>
+      </c>
+      <c r="D229" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الذيد</t>
         </is>
       </c>
       <c r="F229" s="0" t="inlineStr">
@@ -10841,17 +10641,22 @@
     <row r="230">
       <c r="A230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ras Al Khaimah</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B230" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">رأس الخيمة</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C230" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Khatt</t>
+          <t xml:space="preserve">Al Madam</t>
+        </is>
+      </c>
+      <c r="D230" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">المدام</t>
         </is>
       </c>
       <c r="F230" s="0" t="inlineStr">
@@ -10868,17 +10673,17 @@
     <row r="231">
       <c r="A231" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ras Al Khaimah</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B231" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">رأس الخيمة</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C231" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Ghail</t>
+          <t xml:space="preserve">Al Batayah</t>
         </is>
       </c>
       <c r="F231" s="0" t="inlineStr">
@@ -10895,17 +10700,22 @@
     <row r="232">
       <c r="A232" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ras Al Khaimah</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">رأس الخيمة</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C232" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaam</t>
+          <t xml:space="preserve">Kalba</t>
+        </is>
+      </c>
+      <c r="D232" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">كلباء</t>
         </is>
       </c>
       <c r="F232" s="0" t="inlineStr">
@@ -10922,17 +10732,22 @@
     <row r="233">
       <c r="A233" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fujairah</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B233" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الفجيرة</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C233" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fujairah City</t>
+          <t xml:space="preserve">Khorfakkan</t>
+        </is>
+      </c>
+      <c r="D233" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">خورفكان</t>
         </is>
       </c>
       <c r="F233" s="0" t="inlineStr">
@@ -10949,17 +10764,17 @@
     <row r="234">
       <c r="A234" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fujairah</t>
+          <t xml:space="preserve">Sharjah</t>
         </is>
       </c>
       <c r="B234" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الفجيرة</t>
+          <t xml:space="preserve">الشارقة</t>
         </is>
       </c>
       <c r="C234" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Faseel</t>
+          <t xml:space="preserve">Dibba Al Hisn</t>
         </is>
       </c>
       <c r="F234" s="0" t="inlineStr">
@@ -10976,307 +10791,292 @@
     <row r="235">
       <c r="A235" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fujairah</t>
+          <t xml:space="preserve">Ajman</t>
         </is>
       </c>
       <c r="B235" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الفجيرة</t>
+          <t xml:space="preserve">عجمان</t>
         </is>
       </c>
       <c r="C235" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sakamkam</t>
+          <t xml:space="preserve">Al Nuaimiya</t>
+        </is>
+      </c>
+      <c r="D235" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النعيمية</t>
+        </is>
+      </c>
+      <c r="E235" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Nuaimiya 1-3 / Al Nuaimiyah</t>
         </is>
       </c>
       <c r="F235" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G235" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fujairah</t>
+          <t xml:space="preserve">Ajman</t>
         </is>
       </c>
       <c r="B236" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الفجيرة</t>
+          <t xml:space="preserve">عجمان</t>
         </is>
       </c>
       <c r="C236" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Merashid</t>
+          <t xml:space="preserve">Al Rashidiya</t>
+        </is>
+      </c>
+      <c r="D236" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الراشدية</t>
+        </is>
+      </c>
+      <c r="E236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Rashidiya 1-3</t>
         </is>
       </c>
       <c r="F236" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G236" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fujairah</t>
+          <t xml:space="preserve">Ajman</t>
         </is>
       </c>
       <c r="B237" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الفجيرة</t>
+          <t xml:space="preserve">عجمان</t>
         </is>
       </c>
       <c r="C237" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Madhab</t>
+          <t xml:space="preserve">Al Jurf</t>
+        </is>
+      </c>
+      <c r="D237" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الجرف</t>
         </is>
       </c>
       <c r="F237" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G237" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fujairah</t>
+          <t xml:space="preserve">Ajman</t>
         </is>
       </c>
       <c r="B238" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الفجيرة</t>
+          <t xml:space="preserve">عجمان</t>
         </is>
       </c>
       <c r="C238" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Gurfa</t>
+          <t xml:space="preserve">Ajman Corniche</t>
         </is>
       </c>
       <c r="F238" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G238" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fujairah</t>
+          <t xml:space="preserve">Ajman</t>
         </is>
       </c>
       <c r="B239" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الفجيرة</t>
+          <t xml:space="preserve">عجمان</t>
         </is>
       </c>
       <c r="C239" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mirbah</t>
+          <t xml:space="preserve">Ajman Downtown</t>
         </is>
       </c>
       <c r="F239" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G239" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fujairah</t>
+          <t xml:space="preserve">Ajman</t>
         </is>
       </c>
       <c r="B240" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الفجيرة</t>
+          <t xml:space="preserve">عجمان</t>
         </is>
       </c>
       <c r="C240" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qidfa</t>
+          <t xml:space="preserve">Al Mowaihat</t>
+        </is>
+      </c>
+      <c r="D240" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">المويهات</t>
+        </is>
+      </c>
+      <c r="E240" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Mowaihat 1-3 / Al Mowaihat</t>
         </is>
       </c>
       <c r="F240" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G240" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fujairah</t>
+          <t xml:space="preserve">Ajman</t>
         </is>
       </c>
       <c r="B241" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الفجيرة</t>
+          <t xml:space="preserve">عجمان</t>
         </is>
       </c>
       <c r="C241" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Bidiyah</t>
+          <t xml:space="preserve">Al Hamidiya</t>
+        </is>
+      </c>
+      <c r="D241" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الحميدية</t>
         </is>
       </c>
       <c r="F241" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G241" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fujairah</t>
+          <t xml:space="preserve">Ajman</t>
         </is>
       </c>
       <c r="B242" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الفجيرة</t>
+          <t xml:space="preserve">عجمان</t>
         </is>
       </c>
       <c r="C242" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Hail</t>
+          <t xml:space="preserve">Al Rawda</t>
+        </is>
+      </c>
+      <c r="D242" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الروضة</t>
+        </is>
+      </c>
+      <c r="E242" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Rawda 1-3</t>
         </is>
       </c>
       <c r="F242" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G242" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fujairah</t>
+          <t xml:space="preserve">Ajman</t>
         </is>
       </c>
       <c r="B243" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الفجيرة</t>
+          <t xml:space="preserve">عجمان</t>
         </is>
       </c>
       <c r="C243" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Taween</t>
+          <t xml:space="preserve">Emirates City</t>
         </is>
       </c>
       <c r="F243" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G243" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fujairah</t>
+          <t xml:space="preserve">Ajman</t>
         </is>
       </c>
       <c r="B244" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الفجيرة</t>
+          <t xml:space="preserve">عجمان</t>
         </is>
       </c>
       <c r="C244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Masafi</t>
-        </is>
-      </c>
-      <c r="D244" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">مسافي</t>
+          <t xml:space="preserve">Al Zahya</t>
         </is>
       </c>
       <c r="F244" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G244" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fujairah</t>
+          <t xml:space="preserve">Ajman</t>
         </is>
       </c>
       <c r="B245" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الفجيرة</t>
+          <t xml:space="preserve">عجمان</t>
         </is>
       </c>
       <c r="C245" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dibba Al Fujairah</t>
-        </is>
-      </c>
-      <c r="D245" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">دبا الفجيرة</t>
+          <t xml:space="preserve">Al Yasmeen</t>
         </is>
       </c>
       <c r="F245" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G245" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
@@ -11293,219 +11093,2474 @@
       </c>
       <c r="C246" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any other area in this emirate)</t>
+          <t xml:space="preserve">Al Nakheel</t>
         </is>
       </c>
       <c r="F246" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Zone A</t>
-        </is>
-      </c>
-      <c r="G246" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Emirate default: the emirate alone is enough.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umm Al Quwain</t>
+          <t xml:space="preserve">Ajman</t>
         </is>
       </c>
       <c r="B247" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">أم القيوين</t>
+          <t xml:space="preserve">عجمان</t>
         </is>
       </c>
       <c r="C247" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any other area in this emirate)</t>
+          <t xml:space="preserve">Al Rumailah</t>
+        </is>
+      </c>
+      <c r="D247" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الرميلة</t>
         </is>
       </c>
       <c r="F247" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone B</t>
-        </is>
-      </c>
-      <c r="G247" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Emirate default: the emirate alone is enough.</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ras Al Khaimah</t>
+          <t xml:space="preserve">Ajman</t>
         </is>
       </c>
       <c r="B248" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">رأس الخيمة</t>
+          <t xml:space="preserve">عجمان</t>
         </is>
       </c>
       <c r="C248" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any other area in this emirate)</t>
+          <t xml:space="preserve">Al Bustan</t>
         </is>
       </c>
       <c r="F248" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G248" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Emirate default: the emirate alone is enough.</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fujairah</t>
+          <t xml:space="preserve">Ajman</t>
         </is>
       </c>
       <c r="B249" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الفجيرة</t>
+          <t xml:space="preserve">عجمان</t>
         </is>
       </c>
       <c r="C249" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">(any other area in this emirate)</t>
+          <t xml:space="preserve">Al Sawan</t>
         </is>
       </c>
       <c r="F249" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zone D</t>
-        </is>
-      </c>
-      <c r="G249" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Emirate default: the emirate alone is enough.</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Ajman</t>
         </is>
       </c>
       <c r="B250" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">عجمان</t>
         </is>
       </c>
       <c r="C250" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Zubair</t>
-        </is>
-      </c>
-      <c r="D250" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الزبير</t>
+          <t xml:space="preserve">Al Mushairef</t>
         </is>
       </c>
       <c r="F250" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASK</t>
-        </is>
-      </c>
-      <c r="G250" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Price verification required (owner decision 8 Oct 2026): no online price until the owner adds it.</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Ajman</t>
         </is>
       </c>
       <c r="B251" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">عجمان</t>
         </is>
       </c>
       <c r="C251" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Mahatta</t>
-        </is>
-      </c>
-      <c r="D251" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">المحطة</t>
+          <t xml:space="preserve">Al Helio</t>
         </is>
       </c>
       <c r="F251" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASK</t>
-        </is>
-      </c>
-      <c r="G251" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Price verification required (owner decision 8 Oct 2026): no online price until the owner adds it.</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sharjah</t>
+          <t xml:space="preserve">Ajman</t>
         </is>
       </c>
       <c r="B252" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">الشارقة</t>
+          <t xml:space="preserve">عجمان</t>
         </is>
       </c>
       <c r="C252" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Al Ghafiya</t>
-        </is>
-      </c>
-      <c r="D252" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الغافية</t>
+          <t xml:space="preserve">Al Alia</t>
         </is>
       </c>
       <c r="F252" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASK</t>
-        </is>
-      </c>
-      <c r="G252" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Price verification required (owner decision 8 Oct 2026): no online price until the owner adds it.</t>
+          <t xml:space="preserve">Zone A</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ajman</t>
+        </is>
+      </c>
+      <c r="B253" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عجمان</t>
+        </is>
+      </c>
+      <c r="C253" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Tallah</t>
+        </is>
+      </c>
+      <c r="F253" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone A</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ajman</t>
+        </is>
+      </c>
+      <c r="B254" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عجمان</t>
+        </is>
+      </c>
+      <c r="C254" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Amerah</t>
+        </is>
+      </c>
+      <c r="F254" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone A</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ajman</t>
+        </is>
+      </c>
+      <c r="B255" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عجمان</t>
+        </is>
+      </c>
+      <c r="C255" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Hamriya (Ajman)</t>
+        </is>
+      </c>
+      <c r="F255" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone A</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ajman</t>
+        </is>
+      </c>
+      <c r="B256" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عجمان</t>
+        </is>
+      </c>
+      <c r="C256" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Zorah</t>
+        </is>
+      </c>
+      <c r="D256" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الزوراء</t>
+        </is>
+      </c>
+      <c r="F256" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone A</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ajman</t>
+        </is>
+      </c>
+      <c r="B257" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عجمان</t>
+        </is>
+      </c>
+      <c r="C257" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Garden City</t>
+        </is>
+      </c>
+      <c r="F257" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone A</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ajman</t>
+        </is>
+      </c>
+      <c r="B258" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عجمان</t>
+        </is>
+      </c>
+      <c r="C258" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ajman Uptown</t>
+        </is>
+      </c>
+      <c r="F258" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone A</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ajman</t>
+        </is>
+      </c>
+      <c r="B259" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عجمان</t>
+        </is>
+      </c>
+      <c r="C259" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ajman Industrial Area</t>
+        </is>
+      </c>
+      <c r="F259" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone A</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ajman</t>
+        </is>
+      </c>
+      <c r="B260" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عجمان</t>
+        </is>
+      </c>
+      <c r="C260" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Karama (Ajman)</t>
+        </is>
+      </c>
+      <c r="F260" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone A</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ajman</t>
+        </is>
+      </c>
+      <c r="B261" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عجمان</t>
+        </is>
+      </c>
+      <c r="C261" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Raqaib</t>
+        </is>
+      </c>
+      <c r="F261" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone A</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ajman</t>
+        </is>
+      </c>
+      <c r="B262" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عجمان</t>
+        </is>
+      </c>
+      <c r="C262" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Owan</t>
+        </is>
+      </c>
+      <c r="F262" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone A</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ajman</t>
+        </is>
+      </c>
+      <c r="B263" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عجمان</t>
+        </is>
+      </c>
+      <c r="C263" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Muntazi</t>
+        </is>
+      </c>
+      <c r="F263" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone A</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ajman</t>
+        </is>
+      </c>
+      <c r="B264" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عجمان</t>
+        </is>
+      </c>
+      <c r="C264" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liwara</t>
+        </is>
+      </c>
+      <c r="F264" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone A</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ajman</t>
+        </is>
+      </c>
+      <c r="B265" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عجمان</t>
+        </is>
+      </c>
+      <c r="C265" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Butain</t>
+        </is>
+      </c>
+      <c r="F265" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone A</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ajman</t>
+        </is>
+      </c>
+      <c r="B266" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عجمان</t>
+        </is>
+      </c>
+      <c r="C266" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ajman Marina</t>
+        </is>
+      </c>
+      <c r="F266" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone A</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ajman</t>
+        </is>
+      </c>
+      <c r="B267" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عجمان</t>
+        </is>
+      </c>
+      <c r="C267" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Masfout</t>
+        </is>
+      </c>
+      <c r="D267" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مصفوت</t>
+        </is>
+      </c>
+      <c r="F267" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G267" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ajman</t>
+        </is>
+      </c>
+      <c r="B268" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عجمان</t>
+        </is>
+      </c>
+      <c r="C268" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manama</t>
+        </is>
+      </c>
+      <c r="D268" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">المنامة</t>
+        </is>
+      </c>
+      <c r="F268" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G268" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umm Al Quwain</t>
+        </is>
+      </c>
+      <c r="B269" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أم القيوين</t>
+        </is>
+      </c>
+      <c r="C269" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umm Al Quwain City</t>
+        </is>
+      </c>
+      <c r="F269" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone B</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umm Al Quwain</t>
+        </is>
+      </c>
+      <c r="B270" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أم القيوين</t>
+        </is>
+      </c>
+      <c r="C270" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Salamah</t>
+        </is>
+      </c>
+      <c r="F270" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone B</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umm Al Quwain</t>
+        </is>
+      </c>
+      <c r="B271" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أم القيوين</t>
+        </is>
+      </c>
+      <c r="C271" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Raas</t>
+        </is>
+      </c>
+      <c r="F271" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone B</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umm Al Quwain</t>
+        </is>
+      </c>
+      <c r="B272" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أم القيوين</t>
+        </is>
+      </c>
+      <c r="C272" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Haditha</t>
+        </is>
+      </c>
+      <c r="F272" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone B</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umm Al Quwain</t>
+        </is>
+      </c>
+      <c r="B273" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أم القيوين</t>
+        </is>
+      </c>
+      <c r="C273" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Riqqah</t>
+        </is>
+      </c>
+      <c r="F273" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone B</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umm Al Quwain</t>
+        </is>
+      </c>
+      <c r="B274" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أم القيوين</t>
+        </is>
+      </c>
+      <c r="C274" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Ramlah</t>
+        </is>
+      </c>
+      <c r="F274" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone B</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umm Al Quwain</t>
+        </is>
+      </c>
+      <c r="B275" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أم القيوين</t>
+        </is>
+      </c>
+      <c r="C275" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Humrah</t>
+        </is>
+      </c>
+      <c r="F275" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone B</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umm Al Quwain</t>
+        </is>
+      </c>
+      <c r="B276" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أم القيوين</t>
+        </is>
+      </c>
+      <c r="C276" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Dar Al Baida</t>
+        </is>
+      </c>
+      <c r="F276" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone B</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umm Al Quwain</t>
+        </is>
+      </c>
+      <c r="B277" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أم القيوين</t>
+        </is>
+      </c>
+      <c r="C277" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAQ Marina</t>
+        </is>
+      </c>
+      <c r="F277" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone B</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umm Al Quwain</t>
+        </is>
+      </c>
+      <c r="B278" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أم القيوين</t>
+        </is>
+      </c>
+      <c r="C278" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emirates Modern Industrial Area</t>
+        </is>
+      </c>
+      <c r="F278" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone B</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umm Al Quwain</t>
+        </is>
+      </c>
+      <c r="B279" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أم القيوين</t>
+        </is>
+      </c>
+      <c r="C279" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Khor</t>
+        </is>
+      </c>
+      <c r="F279" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone B</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umm Al Quwain</t>
+        </is>
+      </c>
+      <c r="B280" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أم القيوين</t>
+        </is>
+      </c>
+      <c r="C280" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Abraq</t>
+        </is>
+      </c>
+      <c r="F280" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone B</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umm Al Quwain</t>
+        </is>
+      </c>
+      <c r="B281" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أم القيوين</t>
+        </is>
+      </c>
+      <c r="C281" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Maidan</t>
+        </is>
+      </c>
+      <c r="F281" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone B</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umm Al Quwain</t>
+        </is>
+      </c>
+      <c r="B282" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أم القيوين</t>
+        </is>
+      </c>
+      <c r="C282" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Surrah</t>
+        </is>
+      </c>
+      <c r="F282" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone B</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umm Al Quwain</t>
+        </is>
+      </c>
+      <c r="B283" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أم القيوين</t>
+        </is>
+      </c>
+      <c r="C283" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Rafaah</t>
+        </is>
+      </c>
+      <c r="F283" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone B</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umm Al Quwain</t>
+        </is>
+      </c>
+      <c r="B284" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أم القيوين</t>
+        </is>
+      </c>
+      <c r="C284" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Salam City</t>
+        </is>
+      </c>
+      <c r="F284" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone B</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umm Al Quwain</t>
+        </is>
+      </c>
+      <c r="B285" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أم القيوين</t>
+        </is>
+      </c>
+      <c r="C285" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Madar</t>
+        </is>
+      </c>
+      <c r="F285" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone B</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umm Al Quwain</t>
+        </is>
+      </c>
+      <c r="B286" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أم القيوين</t>
+        </is>
+      </c>
+      <c r="C286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Aahad</t>
+        </is>
+      </c>
+      <c r="F286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone B</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umm Al Quwain</t>
+        </is>
+      </c>
+      <c r="B287" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أم القيوين</t>
+        </is>
+      </c>
+      <c r="C287" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Shabiya</t>
+        </is>
+      </c>
+      <c r="F287" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone B</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umm Al Quwain</t>
+        </is>
+      </c>
+      <c r="B288" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أم القيوين</t>
+        </is>
+      </c>
+      <c r="C288" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Hawiyah</t>
+        </is>
+      </c>
+      <c r="F288" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone B</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umm Al Quwain</t>
+        </is>
+      </c>
+      <c r="B289" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أم القيوين</t>
+        </is>
+      </c>
+      <c r="C289" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falaj Al Mualla</t>
+        </is>
+      </c>
+      <c r="D289" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">فلج المعلا</t>
+        </is>
+      </c>
+      <c r="F289" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G289" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B290" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah City</t>
+        </is>
+      </c>
+      <c r="F290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B291" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C291" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Nakheel</t>
+        </is>
+      </c>
+      <c r="F291" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G291" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B292" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Dhait</t>
+        </is>
+      </c>
+      <c r="F292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B293" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C293" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Mairid</t>
+        </is>
+      </c>
+      <c r="F293" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G293" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B294" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C294" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Uraibi</t>
+        </is>
+      </c>
+      <c r="F294" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G294" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B295" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C295" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khuzam</t>
+        </is>
+      </c>
+      <c r="F295" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G295" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B296" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C296" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Qusaidat</t>
+        </is>
+      </c>
+      <c r="F296" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G296" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B297" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C297" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Hamra Village</t>
+        </is>
+      </c>
+      <c r="F297" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G297" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B298" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C298" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mina Al Arab</t>
+        </is>
+      </c>
+      <c r="F298" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G298" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B299" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C299" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Jazirah Al Hamra</t>
+        </is>
+      </c>
+      <c r="D299" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الجزيرة الحمراء</t>
+        </is>
+      </c>
+      <c r="F299" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G299" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B300" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C300" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Rams</t>
+        </is>
+      </c>
+      <c r="D300" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الرمس</t>
+        </is>
+      </c>
+      <c r="F300" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G300" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B301" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C301" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Digdaga</t>
+        </is>
+      </c>
+      <c r="F301" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G301" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B302" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C302" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khatt</t>
+        </is>
+      </c>
+      <c r="F302" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G302" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B303" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C303" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Ghail</t>
+        </is>
+      </c>
+      <c r="F303" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G303" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B304" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C304" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shaam</t>
+        </is>
+      </c>
+      <c r="F304" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G304" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B305" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C305" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Marjan Island</t>
+        </is>
+      </c>
+      <c r="F305" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G305" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B306" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C306" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Seer</t>
+        </is>
+      </c>
+      <c r="F306" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G306" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B307" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C307" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Mamourah</t>
+        </is>
+      </c>
+      <c r="F307" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G307" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B308" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C308" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Qurm</t>
+        </is>
+      </c>
+      <c r="F308" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G308" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B309" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C309" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dafan Al Nakheel</t>
+        </is>
+      </c>
+      <c r="F309" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G309" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B310" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C310" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Julphar</t>
+        </is>
+      </c>
+      <c r="F310" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G310" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B311" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C311" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Hudaibah</t>
+        </is>
+      </c>
+      <c r="F311" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G311" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B312" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C312" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Riffa</t>
+        </is>
+      </c>
+      <c r="F312" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G312" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B313" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C313" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Kharran</t>
+        </is>
+      </c>
+      <c r="F313" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G313" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B314" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C314" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Fahlain</t>
+        </is>
+      </c>
+      <c r="F314" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G314" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B315" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C315" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suhaila</t>
+        </is>
+      </c>
+      <c r="F315" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G315" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B316" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C316" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ghalilah</t>
+        </is>
+      </c>
+      <c r="F316" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G316" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fujairah</t>
+        </is>
+      </c>
+      <c r="B317" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفجيرة</t>
+        </is>
+      </c>
+      <c r="C317" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fujairah City</t>
+        </is>
+      </c>
+      <c r="F317" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G317" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fujairah</t>
+        </is>
+      </c>
+      <c r="B318" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفجيرة</t>
+        </is>
+      </c>
+      <c r="C318" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Faseel</t>
+        </is>
+      </c>
+      <c r="F318" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G318" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fujairah</t>
+        </is>
+      </c>
+      <c r="B319" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفجيرة</t>
+        </is>
+      </c>
+      <c r="C319" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sakamkam</t>
+        </is>
+      </c>
+      <c r="F319" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G319" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fujairah</t>
+        </is>
+      </c>
+      <c r="B320" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفجيرة</t>
+        </is>
+      </c>
+      <c r="C320" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merashid</t>
+        </is>
+      </c>
+      <c r="F320" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G320" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fujairah</t>
+        </is>
+      </c>
+      <c r="B321" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفجيرة</t>
+        </is>
+      </c>
+      <c r="C321" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Madhab</t>
+        </is>
+      </c>
+      <c r="F321" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G321" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fujairah</t>
+        </is>
+      </c>
+      <c r="B322" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفجيرة</t>
+        </is>
+      </c>
+      <c r="C322" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Gurfa</t>
+        </is>
+      </c>
+      <c r="F322" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G322" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fujairah</t>
+        </is>
+      </c>
+      <c r="B323" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفجيرة</t>
+        </is>
+      </c>
+      <c r="C323" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mirbah</t>
+        </is>
+      </c>
+      <c r="F323" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G323" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fujairah</t>
+        </is>
+      </c>
+      <c r="B324" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفجيرة</t>
+        </is>
+      </c>
+      <c r="C324" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qidfa</t>
+        </is>
+      </c>
+      <c r="F324" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G324" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fujairah</t>
+        </is>
+      </c>
+      <c r="B325" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفجيرة</t>
+        </is>
+      </c>
+      <c r="C325" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Bidiyah</t>
+        </is>
+      </c>
+      <c r="F325" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G325" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fujairah</t>
+        </is>
+      </c>
+      <c r="B326" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفجيرة</t>
+        </is>
+      </c>
+      <c r="C326" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Hail</t>
+        </is>
+      </c>
+      <c r="F326" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G326" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fujairah</t>
+        </is>
+      </c>
+      <c r="B327" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفجيرة</t>
+        </is>
+      </c>
+      <c r="C327" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Taween</t>
+        </is>
+      </c>
+      <c r="F327" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G327" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fujairah</t>
+        </is>
+      </c>
+      <c r="B328" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفجيرة</t>
+        </is>
+      </c>
+      <c r="C328" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Masafi</t>
+        </is>
+      </c>
+      <c r="D328" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">مسافي</t>
+        </is>
+      </c>
+      <c r="F328" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G328" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fujairah</t>
+        </is>
+      </c>
+      <c r="B329" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفجيرة</t>
+        </is>
+      </c>
+      <c r="C329" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dibba Al Fujairah</t>
+        </is>
+      </c>
+      <c r="D329" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">دبا الفجيرة</t>
+        </is>
+      </c>
+      <c r="F329" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G329" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fujairah</t>
+        </is>
+      </c>
+      <c r="B330" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفجيرة</t>
+        </is>
+      </c>
+      <c r="C330" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Sharyah</t>
+        </is>
+      </c>
+      <c r="F330" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G330" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fujairah</t>
+        </is>
+      </c>
+      <c r="B331" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفجيرة</t>
+        </is>
+      </c>
+      <c r="C331" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Hilal City</t>
+        </is>
+      </c>
+      <c r="F331" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G331" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fujairah</t>
+        </is>
+      </c>
+      <c r="B332" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفجيرة</t>
+        </is>
+      </c>
+      <c r="C332" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rugaylat</t>
+        </is>
+      </c>
+      <c r="F332" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G332" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fujairah</t>
+        </is>
+      </c>
+      <c r="B333" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفجيرة</t>
+        </is>
+      </c>
+      <c r="C333" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Qurayyah</t>
+        </is>
+      </c>
+      <c r="F333" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G333" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fujairah</t>
+        </is>
+      </c>
+      <c r="B334" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفجيرة</t>
+        </is>
+      </c>
+      <c r="C334" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Aqah</t>
+        </is>
+      </c>
+      <c r="F334" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G334" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fujairah</t>
+        </is>
+      </c>
+      <c r="B335" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفجيرة</t>
+        </is>
+      </c>
+      <c r="C335" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sambraid</t>
+        </is>
+      </c>
+      <c r="F335" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G335" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fujairah</t>
+        </is>
+      </c>
+      <c r="B336" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفجيرة</t>
+        </is>
+      </c>
+      <c r="C336" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thoban</t>
+        </is>
+      </c>
+      <c r="F336" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G336" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fujairah</t>
+        </is>
+      </c>
+      <c r="B337" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفجيرة</t>
+        </is>
+      </c>
+      <c r="C337" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rul Dadna</t>
+        </is>
+      </c>
+      <c r="F337" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G337" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fujairah</t>
+        </is>
+      </c>
+      <c r="B338" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفجيرة</t>
+        </is>
+      </c>
+      <c r="C338" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Al Owaid</t>
+        </is>
+      </c>
+      <c r="F338" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G338" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4-hour minimum (no 3-hour package).</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ajman</t>
+        </is>
+      </c>
+      <c r="B339" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عجمان</t>
+        </is>
+      </c>
+      <c r="C339" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any other area in this emirate)</t>
+        </is>
+      </c>
+      <c r="F339" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone A</t>
+        </is>
+      </c>
+      <c r="G339" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emirate default: the emirate alone is enough.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Umm Al Quwain</t>
+        </is>
+      </c>
+      <c r="B340" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أم القيوين</t>
+        </is>
+      </c>
+      <c r="C340" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any other area in this emirate)</t>
+        </is>
+      </c>
+      <c r="F340" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone B</t>
+        </is>
+      </c>
+      <c r="G340" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emirate default: the emirate alone is enough.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ras Al Khaimah</t>
+        </is>
+      </c>
+      <c r="B341" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رأس الخيمة</t>
+        </is>
+      </c>
+      <c r="C341" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any other area in this emirate)</t>
+        </is>
+      </c>
+      <c r="F341" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G341" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emirate default: the emirate alone is enough.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fujairah</t>
+        </is>
+      </c>
+      <c r="B342" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الفجيرة</t>
+        </is>
+      </c>
+      <c r="C342" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(any other area in this emirate)</t>
+        </is>
+      </c>
+      <c r="F342" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zone D</t>
+        </is>
+      </c>
+      <c r="G342" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emirate default: the emirate alone is enough.</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Abu Dhabi / Al Ain</t>
         </is>
       </c>
-      <c r="B253" s="6" t="inlineStr">
+      <c r="B343" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">أبوظبي / العين</t>
         </is>
       </c>
-      <c r="C253" s="0" t="inlineStr">
+      <c r="C343" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">(all areas)</t>
         </is>
       </c>
-      <c r="F253" s="0" t="inlineStr">
+      <c r="F343" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">NOT ONLINE</t>
         </is>
       </c>
-      <c r="G253" s="0" t="inlineStr">
+      <c r="G343" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Minimum AED 1,000, quoted by the specialist on WhatsApp +971 50 767 7282. Do not offer online booking.</t>
         </is>
@@ -11916,7 +13971,7 @@
         </is>
       </c>
       <c r="B7" s="0" t="str">
-        <f>IFERROR(INDEX('3 Zones &amp; Areas'!$F$5:$F$253,MATCH($B$4,'3 Zones &amp; Areas'!$C$5:$C$253,0)),"Area not listed - price on request")</f>
+        <f>IFERROR(INDEX('3 Zones &amp; Areas'!$F$5:$F$343,MATCH($B$4,'3 Zones &amp; Areas'!$C$5:$C$343,0)),"Area not listed - price on request")</f>
         <v>Zone A</v>
       </c>
     </row>
